--- a/web/public/forms/chg-hyeobui.xlsx
+++ b/web/public/forms/chg-hyeobui.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="협의단가 산정서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'협의단가 산정서'!$A$1:$X$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'협의단가 산정서'!$A$1:$X$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="0.000%;[Red]-0.000%;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.###;[Red]-#,##0.###;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="167" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +39,48 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +89,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F8FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +118,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,32 +143,65 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,6 +568,904 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:X36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>협 의 단 가 산 정 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  계약번호</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  관련 실정보고</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  낙 찰 률</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="6" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>품명·규격</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>① 변경 당시 단가</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>② ①×낙찰률</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>중간값 (①+②)÷2</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>협의 단가</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="12">
+        <f>IF(J11="","",INT(ROUND(J11*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="12">
+        <f>IF(J11="","",INT(ROUND((J11+M11)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="11" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="12">
+        <f>IF(OR(H11="",J11=""),"",INT(ROUND(H11*IF(S11="",P11,S11),6)))</f>
+        <v/>
+      </c>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="12">
+        <f>IF(J12="","",INT(ROUND(J12*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="12">
+        <f>IF(J12="","",INT(ROUND((J12+M12)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="11" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="12">
+        <f>IF(OR(H12="",J12=""),"",INT(ROUND(H12*IF(S12="",P12,S12),6)))</f>
+        <v/>
+      </c>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="12">
+        <f>IF(J13="","",INT(ROUND(J13*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="12">
+        <f>IF(J13="","",INT(ROUND((J13+M13)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="11" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="12">
+        <f>IF(OR(H13="",J13=""),"",INT(ROUND(H13*IF(S13="",P13,S13),6)))</f>
+        <v/>
+      </c>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="12">
+        <f>IF(J14="","",INT(ROUND(J14*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="12">
+        <f>IF(J14="","",INT(ROUND((J14+M14)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="11" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="12">
+        <f>IF(OR(H14="",J14=""),"",INT(ROUND(H14*IF(S14="",P14,S14),6)))</f>
+        <v/>
+      </c>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="12">
+        <f>IF(J15="","",INT(ROUND(J15*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="12">
+        <f>IF(J15="","",INT(ROUND((J15+M15)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="11" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="12">
+        <f>IF(OR(H15="",J15=""),"",INT(ROUND(H15*IF(S15="",P15,S15),6)))</f>
+        <v/>
+      </c>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="11" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="12">
+        <f>IF(J16="","",INT(ROUND(J16*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="12">
+        <f>IF(J16="","",INT(ROUND((J16+M16)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="11" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="12">
+        <f>IF(OR(H16="",J16=""),"",INT(ROUND(H16*IF(S16="",P16,S16),6)))</f>
+        <v/>
+      </c>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="12">
+        <f>IF(J17="","",INT(ROUND(J17*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="12">
+        <f>IF(J17="","",INT(ROUND((J17+M17)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="11" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="12">
+        <f>IF(OR(H17="",J17=""),"",INT(ROUND(H17*IF(S17="",P17,S17),6)))</f>
+        <v/>
+      </c>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="12">
+        <f>IF(J18="","",INT(ROUND(J18*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="12">
+        <f>IF(J18="","",INT(ROUND((J18+M18)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="11" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="12">
+        <f>IF(OR(H18="",J18=""),"",INT(ROUND(H18*IF(S18="",P18,S18),6)))</f>
+        <v/>
+      </c>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="12">
+        <f>IF(J19="","",INT(ROUND(J19*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="12">
+        <f>IF(J19="","",INT(ROUND((J19+M19)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="11" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="12">
+        <f>IF(OR(H19="",J19=""),"",INT(ROUND(H19*IF(S19="",P19,S19),6)))</f>
+        <v/>
+      </c>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="12">
+        <f>IF(J20="","",INT(ROUND(J20*G8,6)))</f>
+        <v/>
+      </c>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="12">
+        <f>IF(J20="","",INT(ROUND((J20+M20)/2,6)))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="11" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="12">
+        <f>IF(OR(H20="",J20=""),"",INT(ROUND(H20*IF(S20="",P20,S20),6)))</f>
+        <v/>
+      </c>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>합        계</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="14">
+        <f>SUM(V11:V20)</f>
+        <v/>
+      </c>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>※ 협의가 이루어지지 않는 경우의 기준값이 «중간값» 입니다. 협의 결과를 «협의 단가» 에 적습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  협의 일자</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  협의 참석자</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  합의 내용</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="5" t="n"/>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="29" ht="10" customHeight="1"/>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="18" t="inlineStr"/>
+      <c r="K31" s="19" t="inlineStr">
+        <is>
+          <t>시공자</t>
+        </is>
+      </c>
+      <c r="Q31" s="20" t="n"/>
+      <c r="U31" s="21" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="18" t="inlineStr"/>
+      <c r="K32" s="19" t="inlineStr">
+        <is>
+          <t>발주기관</t>
+        </is>
+      </c>
+      <c r="Q32" s="20" t="n"/>
+      <c r="U32" s="21" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="6" customHeight="1"/>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="119">
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="S14:U14"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="V21:X21"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="S17:U17"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="A21:U21"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="G26:X26"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="G25:X25"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="S16:U16"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="S18:U18"/>
+    <mergeCell ref="V20:X20"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A35:X35"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="V18:X18"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="G27:X27"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="V19:X19"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="K32:P32"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="S10:U10"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="S19:U19"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="A23:X23"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="A36:X36"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -530,15 +1495,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
         </is>
       </c>
     </row>
@@ -562,7 +1527,11 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -592,7 +1561,11 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>제2026-0312호</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -622,7 +1595,11 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>실정보고 제3호(2026. 6. 2.)</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -652,7 +1629,9 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="7" t="n">
+        <v>0.87452</v>
+      </c>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -673,7 +1652,7 @@
     </row>
     <row r="9" ht="6" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>품명·규격</t>
         </is>
@@ -682,47 +1661,47 @@
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
       <c r="I10" s="5" t="n"/>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>① 변경 당시 단가</t>
         </is>
       </c>
       <c r="K10" s="5" t="n"/>
       <c r="L10" s="5" t="n"/>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>② ①×낙찰률</t>
         </is>
       </c>
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="5" t="n"/>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="P10" s="8" t="inlineStr">
         <is>
           <t>중간값 (①+②)÷2</t>
         </is>
       </c>
       <c r="Q10" s="5" t="n"/>
       <c r="R10" s="5" t="n"/>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="8" t="inlineStr">
         <is>
           <t>협의 단가</t>
         </is>
       </c>
       <c r="T10" s="5" t="n"/>
       <c r="U10" s="5" t="n"/>
-      <c r="V10" s="7" t="inlineStr">
+      <c r="V10" s="8" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
@@ -731,308 +1710,439 @@
       <c r="X10" s="5" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>PE 이중벽관 D600</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="10" t="n">
+        <v>42</v>
+      </c>
       <c r="I11" s="5" t="n"/>
-      <c r="J11" s="8" t="inlineStr"/>
+      <c r="J11" s="11" t="n">
+        <v>186500</v>
+      </c>
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="n"/>
-      <c r="M11" s="8" t="inlineStr"/>
+      <c r="M11" s="12">
+        <f>IF(J11="","",INT(ROUND(J11*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
-      <c r="P11" s="8" t="inlineStr"/>
+      <c r="P11" s="12">
+        <f>IF(J11="","",INT(ROUND((J11+M11)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
-      <c r="S11" s="8" t="inlineStr"/>
+      <c r="S11" s="11" t="n"/>
       <c r="T11" s="5" t="n"/>
       <c r="U11" s="5" t="n"/>
-      <c r="V11" s="8" t="inlineStr"/>
+      <c r="V11" s="12">
+        <f>IF(OR(H11="",J11=""),"",INT(ROUND(H11*IF(S11="",P11,S11),6)))</f>
+        <v/>
+      </c>
       <c r="W11" s="5" t="n"/>
       <c r="X11" s="5" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>집수정 1.2×1.2</t>
+        </is>
+      </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="I12" s="5" t="n"/>
-      <c r="J12" s="8" t="inlineStr"/>
+      <c r="J12" s="11" t="n">
+        <v>1245000</v>
+      </c>
       <c r="K12" s="5" t="n"/>
       <c r="L12" s="5" t="n"/>
-      <c r="M12" s="8" t="inlineStr"/>
+      <c r="M12" s="12">
+        <f>IF(J12="","",INT(ROUND(J12*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="n"/>
-      <c r="P12" s="8" t="inlineStr"/>
+      <c r="P12" s="12">
+        <f>IF(J12="","",INT(ROUND((J12+M12)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
-      <c r="S12" s="8" t="inlineStr"/>
+      <c r="S12" s="11" t="n"/>
       <c r="T12" s="5" t="n"/>
       <c r="U12" s="5" t="n"/>
-      <c r="V12" s="8" t="inlineStr"/>
+      <c r="V12" s="12">
+        <f>IF(OR(H12="",J12=""),"",INT(ROUND(H12*IF(S12="",P12,S12),6)))</f>
+        <v/>
+      </c>
       <c r="W12" s="5" t="n"/>
       <c r="X12" s="5" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>가물막이(톤마대)</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="10" t="n">
+        <v>60</v>
+      </c>
       <c r="I13" s="5" t="n"/>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="J13" s="11" t="n">
+        <v>38400</v>
+      </c>
       <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="n"/>
-      <c r="M13" s="8" t="inlineStr"/>
+      <c r="M13" s="12">
+        <f>IF(J13="","",INT(ROUND(J13*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
-      <c r="P13" s="8" t="inlineStr"/>
+      <c r="P13" s="12">
+        <f>IF(J13="","",INT(ROUND((J13+M13)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
-      <c r="S13" s="8" t="inlineStr"/>
+      <c r="S13" s="11" t="n">
+        <v>36000</v>
+      </c>
       <c r="T13" s="5" t="n"/>
       <c r="U13" s="5" t="n"/>
-      <c r="V13" s="8" t="inlineStr"/>
+      <c r="V13" s="12">
+        <f>IF(OR(H13="",J13=""),"",INT(ROUND(H13*IF(S13="",P13,S13),6)))</f>
+        <v/>
+      </c>
       <c r="W13" s="5" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="8" t="inlineStr"/>
+      <c r="F14" s="9" t="n"/>
       <c r="G14" s="5" t="n"/>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="H14" s="10" t="n"/>
       <c r="I14" s="5" t="n"/>
-      <c r="J14" s="8" t="inlineStr"/>
+      <c r="J14" s="11" t="n"/>
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
-      <c r="M14" s="8" t="inlineStr"/>
+      <c r="M14" s="12">
+        <f>IF(J14="","",INT(ROUND(J14*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
-      <c r="P14" s="8" t="inlineStr"/>
+      <c r="P14" s="12">
+        <f>IF(J14="","",INT(ROUND((J14+M14)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
-      <c r="S14" s="8" t="inlineStr"/>
+      <c r="S14" s="11" t="n"/>
       <c r="T14" s="5" t="n"/>
       <c r="U14" s="5" t="n"/>
-      <c r="V14" s="8" t="inlineStr"/>
+      <c r="V14" s="12">
+        <f>IF(OR(H14="",J14=""),"",INT(ROUND(H14*IF(S14="",P14,S14),6)))</f>
+        <v/>
+      </c>
       <c r="W14" s="5" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
-      <c r="F15" s="8" t="inlineStr"/>
+      <c r="F15" s="9" t="n"/>
       <c r="G15" s="5" t="n"/>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="10" t="n"/>
       <c r="I15" s="5" t="n"/>
-      <c r="J15" s="8" t="inlineStr"/>
+      <c r="J15" s="11" t="n"/>
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="n"/>
-      <c r="M15" s="8" t="inlineStr"/>
+      <c r="M15" s="12">
+        <f>IF(J15="","",INT(ROUND(J15*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
-      <c r="P15" s="8" t="inlineStr"/>
+      <c r="P15" s="12">
+        <f>IF(J15="","",INT(ROUND((J15+M15)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
-      <c r="S15" s="8" t="inlineStr"/>
+      <c r="S15" s="11" t="n"/>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
-      <c r="V15" s="8" t="inlineStr"/>
+      <c r="V15" s="12">
+        <f>IF(OR(H15="",J15=""),"",INT(ROUND(H15*IF(S15="",P15,S15),6)))</f>
+        <v/>
+      </c>
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
+      <c r="A16" s="9" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="8" t="inlineStr"/>
+      <c r="F16" s="9" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="8" t="inlineStr"/>
+      <c r="H16" s="10" t="n"/>
       <c r="I16" s="5" t="n"/>
-      <c r="J16" s="8" t="inlineStr"/>
+      <c r="J16" s="11" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
-      <c r="M16" s="8" t="inlineStr"/>
+      <c r="M16" s="12">
+        <f>IF(J16="","",INT(ROUND(J16*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
-      <c r="P16" s="8" t="inlineStr"/>
+      <c r="P16" s="12">
+        <f>IF(J16="","",INT(ROUND((J16+M16)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
-      <c r="S16" s="8" t="inlineStr"/>
+      <c r="S16" s="11" t="n"/>
       <c r="T16" s="5" t="n"/>
       <c r="U16" s="5" t="n"/>
-      <c r="V16" s="8" t="inlineStr"/>
+      <c r="V16" s="12">
+        <f>IF(OR(H16="",J16=""),"",INT(ROUND(H16*IF(S16="",P16,S16),6)))</f>
+        <v/>
+      </c>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr"/>
+      <c r="A17" s="9" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="8" t="inlineStr"/>
+      <c r="F17" s="9" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="10" t="n"/>
       <c r="I17" s="5" t="n"/>
-      <c r="J17" s="8" t="inlineStr"/>
+      <c r="J17" s="11" t="n"/>
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
-      <c r="M17" s="8" t="inlineStr"/>
+      <c r="M17" s="12">
+        <f>IF(J17="","",INT(ROUND(J17*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
-      <c r="P17" s="8" t="inlineStr"/>
+      <c r="P17" s="12">
+        <f>IF(J17="","",INT(ROUND((J17+M17)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="5" t="n"/>
-      <c r="S17" s="8" t="inlineStr"/>
+      <c r="S17" s="11" t="n"/>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
-      <c r="V17" s="8" t="inlineStr"/>
+      <c r="V17" s="12">
+        <f>IF(OR(H17="",J17=""),"",INT(ROUND(H17*IF(S17="",P17,S17),6)))</f>
+        <v/>
+      </c>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr"/>
+      <c r="A18" s="9" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="F18" s="9" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="10" t="n"/>
       <c r="I18" s="5" t="n"/>
-      <c r="J18" s="8" t="inlineStr"/>
+      <c r="J18" s="11" t="n"/>
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
-      <c r="M18" s="8" t="inlineStr"/>
+      <c r="M18" s="12">
+        <f>IF(J18="","",INT(ROUND(J18*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
-      <c r="P18" s="8" t="inlineStr"/>
+      <c r="P18" s="12">
+        <f>IF(J18="","",INT(ROUND((J18+M18)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
-      <c r="S18" s="8" t="inlineStr"/>
+      <c r="S18" s="11" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
-      <c r="V18" s="8" t="inlineStr"/>
+      <c r="V18" s="12">
+        <f>IF(OR(H18="",J18=""),"",INT(ROUND(H18*IF(S18="",P18,S18),6)))</f>
+        <v/>
+      </c>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="8" t="inlineStr"/>
+      <c r="F19" s="9" t="n"/>
       <c r="G19" s="5" t="n"/>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="10" t="n"/>
       <c r="I19" s="5" t="n"/>
-      <c r="J19" s="8" t="inlineStr"/>
+      <c r="J19" s="11" t="n"/>
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="5" t="n"/>
-      <c r="M19" s="8" t="inlineStr"/>
+      <c r="M19" s="12">
+        <f>IF(J19="","",INT(ROUND(J19*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
-      <c r="P19" s="8" t="inlineStr"/>
+      <c r="P19" s="12">
+        <f>IF(J19="","",INT(ROUND((J19+M19)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q19" s="5" t="n"/>
       <c r="R19" s="5" t="n"/>
-      <c r="S19" s="8" t="inlineStr"/>
+      <c r="S19" s="11" t="n"/>
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5" t="n"/>
-      <c r="V19" s="8" t="inlineStr"/>
+      <c r="V19" s="12">
+        <f>IF(OR(H19="",J19=""),"",INT(ROUND(H19*IF(S19="",P19,S19),6)))</f>
+        <v/>
+      </c>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
-      <c r="F20" s="8" t="inlineStr"/>
+      <c r="F20" s="9" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="10" t="n"/>
       <c r="I20" s="5" t="n"/>
-      <c r="J20" s="8" t="inlineStr"/>
+      <c r="J20" s="11" t="n"/>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
-      <c r="M20" s="8" t="inlineStr"/>
+      <c r="M20" s="12">
+        <f>IF(J20="","",INT(ROUND(J20*G8,6)))</f>
+        <v/>
+      </c>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
-      <c r="P20" s="8" t="inlineStr"/>
+      <c r="P20" s="12">
+        <f>IF(J20="","",INT(ROUND((J20+M20)/2,6)))</f>
+        <v/>
+      </c>
       <c r="Q20" s="5" t="n"/>
       <c r="R20" s="5" t="n"/>
-      <c r="S20" s="8" t="inlineStr"/>
+      <c r="S20" s="11" t="n"/>
       <c r="T20" s="5" t="n"/>
       <c r="U20" s="5" t="n"/>
-      <c r="V20" s="8" t="inlineStr"/>
+      <c r="V20" s="12">
+        <f>IF(OR(H20="",J20=""),"",INT(ROUND(H20*IF(S20="",P20,S20),6)))</f>
+        <v/>
+      </c>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>합        계</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="14">
+        <f>SUM(V11:V20)</f>
+        <v/>
+      </c>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>※ 협의가 이루어지지 않는 경우의 기준값이 «중간값» 입니다. 협의 결과를 «협의 단가» 에 적습니다.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  협의 일자</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
+    <row r="24" ht="6" customHeight="1"/>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  협의 참석자</t>
+          <t xml:space="preserve">  협의 일자</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
@@ -1040,7 +2150,9 @@
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="inlineStr"/>
+      <c r="G25" s="16" t="n">
+        <v>46185</v>
+      </c>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
@@ -1062,7 +2174,7 @@
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  합의 내용</t>
+          <t xml:space="preserve">  협의 참석자</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
@@ -1070,7 +2182,11 @@
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>가나시 건설과 박감독 · 예시건설(주) 김철수</t>
+        </is>
+      </c>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
@@ -1089,55 +2205,100 @@
       <c r="W26" s="5" t="n"/>
       <c r="X26" s="5" t="n"/>
     </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="10" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="K30" s="11" t="inlineStr">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  합의 내용</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>PE관·집수정은 중간값, 가물막이는 협의 단가 36,000원으로 합의</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="5" t="n"/>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="29" ht="10" customHeight="1"/>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="17" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="18" t="inlineStr"/>
+      <c r="K31" s="19" t="inlineStr">
         <is>
           <t>시공자</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="Q31" s="20" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U31" s="21" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="K31" s="11" t="inlineStr">
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="18" t="inlineStr"/>
+      <c r="K32" s="19" t="inlineStr">
         <is>
           <t>발주기관</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="Q32" s="20" t="inlineStr">
+        <is>
+          <t>박감독</t>
+        </is>
+      </c>
+      <c r="U32" s="21" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="33" ht="6" customHeight="1"/>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="118">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="S14:U14"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="S13:U13"/>
+    <mergeCell ref="K31:P31"/>
     <mergeCell ref="P17:R17"/>
     <mergeCell ref="M12:O12"/>
     <mergeCell ref="J11:L11"/>
@@ -1145,16 +2306,14 @@
     <mergeCell ref="S15:U15"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="P19:R19"/>
+    <mergeCell ref="U31:X31"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="P12:R12"/>
-    <mergeCell ref="K31:R31"/>
-    <mergeCell ref="A29:X29"/>
     <mergeCell ref="P14:R14"/>
     <mergeCell ref="V12:X12"/>
-    <mergeCell ref="S31:X31"/>
     <mergeCell ref="F13:G13"/>
+    <mergeCell ref="V21:X21"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="H15:I15"/>
@@ -1165,21 +2324,22 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="J15:L15"/>
     <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A32:J32"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="M15:O15"/>
     <mergeCell ref="P16:R16"/>
     <mergeCell ref="J16:L16"/>
-    <mergeCell ref="G24:X24"/>
+    <mergeCell ref="A21:U21"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="P18:R18"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="S30:X30"/>
     <mergeCell ref="G26:X26"/>
     <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A22:X22"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="H11:I11"/>
@@ -1190,8 +2350,11 @@
     <mergeCell ref="V17:X17"/>
     <mergeCell ref="P20:R20"/>
     <mergeCell ref="S16:U16"/>
+    <mergeCell ref="U32:X32"/>
     <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A30:X30"/>
     <mergeCell ref="J14:L14"/>
+    <mergeCell ref="Q31:T31"/>
     <mergeCell ref="S18:U18"/>
     <mergeCell ref="V20:X20"/>
     <mergeCell ref="H14:I14"/>
@@ -1213,6 +2376,7 @@
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="J10:L10"/>
     <mergeCell ref="J19:L19"/>
+    <mergeCell ref="G27:X27"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="V19:X19"/>
@@ -1221,11 +2385,12 @@
     <mergeCell ref="P11:R11"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="K30:R30"/>
+    <mergeCell ref="K32:P32"/>
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="J20:L20"/>
     <mergeCell ref="M16:O16"/>
+    <mergeCell ref="Q32:T32"/>
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="F12:G12"/>
@@ -1233,6 +2398,7 @@
     <mergeCell ref="M18:O18"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="P13:R13"/>
+    <mergeCell ref="A23:X23"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="P15:R15"/>
     <mergeCell ref="A17:E17"/>
@@ -1245,7 +2411,8 @@
     <mergeCell ref="M1:X1"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/chg-hyeobui.xlsx
+++ b/web/public/forms/chg-hyeobui.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'협의단가 산정서'!$A$1:$X$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'협의단가 산정서'!$A$1:$X$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -207,6 +207,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="300" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -568,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X36"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -1043,416 +1048,292 @@
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="n"/>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>합        계</t>
+        </is>
+      </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="9" t="n"/>
+      <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="10" t="n"/>
+      <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
-      <c r="J18" s="11" t="n"/>
+      <c r="J18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
-      <c r="M18" s="12">
-        <f>IF(J18="","",INT(ROUND(J18*G8,6)))</f>
-        <v/>
-      </c>
+      <c r="M18" s="5" t="n"/>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
-      <c r="P18" s="12">
-        <f>IF(J18="","",INT(ROUND((J18+M18)/2,6)))</f>
-        <v/>
-      </c>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
-      <c r="S18" s="11" t="n"/>
+      <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
-      <c r="V18" s="12">
-        <f>IF(OR(H18="",J18=""),"",INT(ROUND(H18*IF(S18="",P18,S18),6)))</f>
+      <c r="V18" s="14">
+        <f>SUM(V11:V17)</f>
         <v/>
       </c>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="12">
-        <f>IF(J19="","",INT(ROUND(J19*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="12">
-        <f>IF(J19="","",INT(ROUND((J19+M19)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="11" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="12">
-        <f>IF(OR(H19="",J19=""),"",INT(ROUND(H19*IF(S19="",P19,S19),6)))</f>
-        <v/>
-      </c>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="12">
-        <f>IF(J20="","",INT(ROUND(J20*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="12">
-        <f>IF(J20="","",INT(ROUND((J20+M20)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="11" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="12">
-        <f>IF(OR(H20="",J20=""),"",INT(ROUND(H20*IF(S20="",P20,S20),6)))</f>
-        <v/>
-      </c>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>합        계</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="14">
-        <f>SUM(V11:V20)</f>
-        <v/>
-      </c>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>※ 협의가 이루어지지 않는 경우의 기준값이 «중간값» 입니다. 협의 결과를 «협의 단가» 에 적습니다.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="6" customHeight="1"/>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  협의 일자</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  협의 참석자</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n"/>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="5" t="n"/>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  합의 내용</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="5" t="n"/>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
-    <row r="29" ht="10" customHeight="1"/>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="10" customHeight="1"/>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">          년        월        일</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="18" t="inlineStr"/>
-      <c r="K31" s="19" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="18" t="inlineStr"/>
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <t>시공자</t>
         </is>
       </c>
-      <c r="Q31" s="20" t="n"/>
-      <c r="U31" s="21" t="inlineStr">
+      <c r="Q28" s="20" t="n"/>
+      <c r="U28" s="21" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="18" t="inlineStr"/>
-      <c r="K32" s="19" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="18" t="inlineStr"/>
+      <c r="K29" s="19" t="inlineStr">
         <is>
           <t>발주기관</t>
         </is>
       </c>
-      <c r="Q32" s="20" t="n"/>
-      <c r="U32" s="21" t="inlineStr">
+      <c r="Q29" s="20" t="n"/>
+      <c r="U29" s="21" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="6" customHeight="1"/>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="119">
+  <mergeCells count="95">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="S14:U14"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="S13:U13"/>
-    <mergeCell ref="K31:P31"/>
     <mergeCell ref="P17:R17"/>
+    <mergeCell ref="U29:X29"/>
     <mergeCell ref="M12:O12"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="S15:U15"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="U31:X31"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A32:X32"/>
     <mergeCell ref="P12:R12"/>
     <mergeCell ref="P14:R14"/>
     <mergeCell ref="V12:X12"/>
+    <mergeCell ref="G22:X22"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="V21:X21"/>
     <mergeCell ref="H13:I13"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="V13:X13"/>
     <mergeCell ref="S17:U17"/>
     <mergeCell ref="S11:U11"/>
-    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="G23:X23"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="U28:X28"/>
     <mergeCell ref="J15:L15"/>
     <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A32:J32"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A29:J29"/>
     <mergeCell ref="M15:O15"/>
     <mergeCell ref="P16:R16"/>
     <mergeCell ref="J16:L16"/>
-    <mergeCell ref="A21:U21"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="G26:X26"/>
+    <mergeCell ref="G24:X24"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="G25:X25"/>
-    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="A20:X20"/>
+    <mergeCell ref="Q29:T29"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="V17:X17"/>
-    <mergeCell ref="P20:R20"/>
     <mergeCell ref="S16:U16"/>
-    <mergeCell ref="U32:X32"/>
     <mergeCell ref="H12:I12"/>
-    <mergeCell ref="A30:X30"/>
     <mergeCell ref="J14:L14"/>
-    <mergeCell ref="Q31:T31"/>
-    <mergeCell ref="S18:U18"/>
-    <mergeCell ref="V20:X20"/>
     <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="V15:X15"/>
+    <mergeCell ref="A18:U18"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A27:X27"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="M17:O17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="A33:X33"/>
+    <mergeCell ref="Q28:T28"/>
     <mergeCell ref="V16:X16"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A35:X35"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="K28:P28"/>
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="J17:L17"/>
     <mergeCell ref="S12:U12"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="G27:X27"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="V19:X19"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="P11:R11"/>
-    <mergeCell ref="H20:I20"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="K32:P32"/>
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="G6:X6"/>
-    <mergeCell ref="J20:L20"/>
     <mergeCell ref="M16:O16"/>
-    <mergeCell ref="Q32:T32"/>
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="F12:G12"/>
-    <mergeCell ref="S19:U19"/>
-    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="P13:R13"/>
-    <mergeCell ref="A23:X23"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="P15:R15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="P10:R10"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="M1:X1"/>
-    <mergeCell ref="A36:X36"/>
     <mergeCell ref="G8:X8"/>
+    <mergeCell ref="K29:P29"/>
   </mergeCells>
+  <conditionalFormatting sqref="H11:H17">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(H11),MOD(H11,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1466,7 +1347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -1993,424 +1874,300 @@
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="n"/>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>합        계</t>
+        </is>
+      </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="9" t="n"/>
+      <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="10" t="n"/>
+      <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
-      <c r="J18" s="11" t="n"/>
+      <c r="J18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
-      <c r="M18" s="12">
-        <f>IF(J18="","",INT(ROUND(J18*G8,6)))</f>
-        <v/>
-      </c>
+      <c r="M18" s="5" t="n"/>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
-      <c r="P18" s="12">
-        <f>IF(J18="","",INT(ROUND((J18+M18)/2,6)))</f>
-        <v/>
-      </c>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
-      <c r="S18" s="11" t="n"/>
+      <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
-      <c r="V18" s="12">
-        <f>IF(OR(H18="",J18=""),"",INT(ROUND(H18*IF(S18="",P18,S18),6)))</f>
+      <c r="V18" s="14">
+        <f>SUM(V11:V17)</f>
         <v/>
       </c>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="12">
-        <f>IF(J19="","",INT(ROUND(J19*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="12">
-        <f>IF(J19="","",INT(ROUND((J19+M19)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="11" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="12">
-        <f>IF(OR(H19="",J19=""),"",INT(ROUND(H19*IF(S19="",P19,S19),6)))</f>
-        <v/>
-      </c>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="12">
-        <f>IF(J20="","",INT(ROUND(J20*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="12">
-        <f>IF(J20="","",INT(ROUND((J20+M20)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="11" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="12">
-        <f>IF(OR(H20="",J20=""),"",INT(ROUND(H20*IF(S20="",P20,S20),6)))</f>
-        <v/>
-      </c>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>합        계</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="14">
-        <f>SUM(V11:V20)</f>
-        <v/>
-      </c>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>※ 협의가 이루어지지 않는 경우의 기준값이 «중간값» 입니다. 협의 결과를 «협의 단가» 에 적습니다.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="6" customHeight="1"/>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  협의 일자</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="16" t="n">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="16" t="n">
         <v>46185</v>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  협의 참석자</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>가나시 건설과 박감독 · 예시건설(주) 김철수</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n"/>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="5" t="n"/>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  합의 내용</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>PE관·집수정은 중간값, 가물막이는 협의 단가 36,000원으로 합의</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="5" t="n"/>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
-    <row r="29" ht="10" customHeight="1"/>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="17" t="n">
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="10" customHeight="1"/>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="17" t="n">
         <v>46294</v>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="18" t="inlineStr"/>
-      <c r="K31" s="19" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="18" t="inlineStr"/>
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <t>시공자</t>
         </is>
       </c>
-      <c r="Q31" s="20" t="inlineStr">
+      <c r="Q28" s="20" t="inlineStr">
         <is>
           <t>김철수</t>
         </is>
       </c>
-      <c r="U31" s="21" t="inlineStr">
+      <c r="U28" s="21" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="18" t="inlineStr"/>
-      <c r="K32" s="19" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="18" t="inlineStr"/>
+      <c r="K29" s="19" t="inlineStr">
         <is>
           <t>발주기관</t>
         </is>
       </c>
-      <c r="Q32" s="20" t="inlineStr">
+      <c r="Q29" s="20" t="inlineStr">
         <is>
           <t>박감독</t>
         </is>
       </c>
-      <c r="U32" s="21" t="inlineStr">
+      <c r="U29" s="21" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="6" customHeight="1"/>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="118">
+  <mergeCells count="94">
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="S14:U14"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="S13:U13"/>
-    <mergeCell ref="K31:P31"/>
     <mergeCell ref="P17:R17"/>
+    <mergeCell ref="U29:X29"/>
     <mergeCell ref="M12:O12"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="S15:U15"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="U31:X31"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A32:X32"/>
     <mergeCell ref="P12:R12"/>
     <mergeCell ref="P14:R14"/>
     <mergeCell ref="V12:X12"/>
+    <mergeCell ref="G22:X22"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="V21:X21"/>
     <mergeCell ref="H13:I13"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="V13:X13"/>
     <mergeCell ref="S17:U17"/>
     <mergeCell ref="S11:U11"/>
-    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="G23:X23"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="U28:X28"/>
     <mergeCell ref="J15:L15"/>
     <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A32:J32"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A29:J29"/>
     <mergeCell ref="M15:O15"/>
     <mergeCell ref="P16:R16"/>
     <mergeCell ref="J16:L16"/>
-    <mergeCell ref="A21:U21"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="G26:X26"/>
+    <mergeCell ref="G24:X24"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="G25:X25"/>
-    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="A20:X20"/>
+    <mergeCell ref="Q29:T29"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="V17:X17"/>
-    <mergeCell ref="P20:R20"/>
     <mergeCell ref="S16:U16"/>
-    <mergeCell ref="U32:X32"/>
     <mergeCell ref="H12:I12"/>
-    <mergeCell ref="A30:X30"/>
     <mergeCell ref="J14:L14"/>
-    <mergeCell ref="Q31:T31"/>
-    <mergeCell ref="S18:U18"/>
-    <mergeCell ref="V20:X20"/>
     <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="V15:X15"/>
+    <mergeCell ref="A18:U18"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A27:X27"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="M17:O17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="Q28:T28"/>
     <mergeCell ref="V16:X16"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A35:X35"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="K28:P28"/>
     <mergeCell ref="V18:X18"/>
     <mergeCell ref="J17:L17"/>
     <mergeCell ref="S12:U12"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="G27:X27"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="V19:X19"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="P11:R11"/>
-    <mergeCell ref="H20:I20"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="K32:P32"/>
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="G6:X6"/>
-    <mergeCell ref="J20:L20"/>
     <mergeCell ref="M16:O16"/>
-    <mergeCell ref="Q32:T32"/>
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V11:X11"/>
     <mergeCell ref="F12:G12"/>
-    <mergeCell ref="S19:U19"/>
-    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="P13:R13"/>
-    <mergeCell ref="A23:X23"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="P15:R15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="P10:R10"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="M1:X1"/>
     <mergeCell ref="G8:X8"/>
+    <mergeCell ref="K29:P29"/>
   </mergeCells>
+  <conditionalFormatting sqref="H11:H17">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(H11),MOD(H11,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/web/public/forms/chg-hyeobui.xlsx
+++ b/web/public/forms/chg-hyeobui.xlsx
@@ -605,7 +605,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="23" t="inlineStr">

--- a/web/public/forms/chg-hyeobui.xlsx
+++ b/web/public/forms/chg-hyeobui.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="협의단가 산정서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'협의단가 산정서'!$A$1:$X$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -134,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -199,19 +197,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <numFmt numFmtId="300" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -815,25 +805,16 @@
       <c r="J11" s="11" t="n"/>
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="n"/>
-      <c r="M11" s="12">
-        <f>IF(J11="","",INT(ROUND(J11*G8,6)))</f>
-        <v/>
-      </c>
+      <c r="M11" s="12" t="n"/>
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
-      <c r="P11" s="12">
-        <f>IF(J11="","",INT(ROUND((J11+M11)/2,6)))</f>
-        <v/>
-      </c>
+      <c r="P11" s="12" t="n"/>
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="11" t="n"/>
       <c r="T11" s="5" t="n"/>
       <c r="U11" s="5" t="n"/>
-      <c r="V11" s="12">
-        <f>IF(OR(H11="",J11=""),"",INT(ROUND(H11*IF(S11="",P11,S11),6)))</f>
-        <v/>
-      </c>
+      <c r="V11" s="12" t="n"/>
       <c r="W11" s="5" t="n"/>
       <c r="X11" s="5" t="n"/>
     </row>
@@ -850,25 +831,16 @@
       <c r="J12" s="11" t="n"/>
       <c r="K12" s="5" t="n"/>
       <c r="L12" s="5" t="n"/>
-      <c r="M12" s="12">
-        <f>IF(J12="","",INT(ROUND(J12*G8,6)))</f>
-        <v/>
-      </c>
+      <c r="M12" s="12" t="n"/>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="n"/>
-      <c r="P12" s="12">
-        <f>IF(J12="","",INT(ROUND((J12+M12)/2,6)))</f>
-        <v/>
-      </c>
+      <c r="P12" s="12" t="n"/>
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="11" t="n"/>
       <c r="T12" s="5" t="n"/>
       <c r="U12" s="5" t="n"/>
-      <c r="V12" s="12">
-        <f>IF(OR(H12="",J12=""),"",INT(ROUND(H12*IF(S12="",P12,S12),6)))</f>
-        <v/>
-      </c>
+      <c r="V12" s="12" t="n"/>
       <c r="W12" s="5" t="n"/>
       <c r="X12" s="5" t="n"/>
     </row>
@@ -885,25 +857,16 @@
       <c r="J13" s="11" t="n"/>
       <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="n"/>
-      <c r="M13" s="12">
-        <f>IF(J13="","",INT(ROUND(J13*G8,6)))</f>
-        <v/>
-      </c>
+      <c r="M13" s="12" t="n"/>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
-      <c r="P13" s="12">
-        <f>IF(J13="","",INT(ROUND((J13+M13)/2,6)))</f>
-        <v/>
-      </c>
+      <c r="P13" s="12" t="n"/>
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="11" t="n"/>
       <c r="T13" s="5" t="n"/>
       <c r="U13" s="5" t="n"/>
-      <c r="V13" s="12">
-        <f>IF(OR(H13="",J13=""),"",INT(ROUND(H13*IF(S13="",P13,S13),6)))</f>
-        <v/>
-      </c>
+      <c r="V13" s="12" t="n"/>
       <c r="W13" s="5" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
@@ -920,25 +883,16 @@
       <c r="J14" s="11" t="n"/>
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
-      <c r="M14" s="12">
-        <f>IF(J14="","",INT(ROUND(J14*G8,6)))</f>
-        <v/>
-      </c>
+      <c r="M14" s="12" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
-      <c r="P14" s="12">
-        <f>IF(J14="","",INT(ROUND((J14+M14)/2,6)))</f>
-        <v/>
-      </c>
+      <c r="P14" s="12" t="n"/>
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="11" t="n"/>
       <c r="T14" s="5" t="n"/>
       <c r="U14" s="5" t="n"/>
-      <c r="V14" s="12">
-        <f>IF(OR(H14="",J14=""),"",INT(ROUND(H14*IF(S14="",P14,S14),6)))</f>
-        <v/>
-      </c>
+      <c r="V14" s="12" t="n"/>
       <c r="W14" s="5" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
@@ -955,25 +909,16 @@
       <c r="J15" s="11" t="n"/>
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="n"/>
-      <c r="M15" s="12">
-        <f>IF(J15="","",INT(ROUND(J15*G8,6)))</f>
-        <v/>
-      </c>
+      <c r="M15" s="12" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
-      <c r="P15" s="12">
-        <f>IF(J15="","",INT(ROUND((J15+M15)/2,6)))</f>
-        <v/>
-      </c>
+      <c r="P15" s="12" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="11" t="n"/>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
-      <c r="V15" s="12">
-        <f>IF(OR(H15="",J15=""),"",INT(ROUND(H15*IF(S15="",P15,S15),6)))</f>
-        <v/>
-      </c>
+      <c r="V15" s="12" t="n"/>
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
@@ -990,25 +935,16 @@
       <c r="J16" s="11" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
-      <c r="M16" s="12">
-        <f>IF(J16="","",INT(ROUND(J16*G8,6)))</f>
-        <v/>
-      </c>
+      <c r="M16" s="12" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
-      <c r="P16" s="12">
-        <f>IF(J16="","",INT(ROUND((J16+M16)/2,6)))</f>
-        <v/>
-      </c>
+      <c r="P16" s="12" t="n"/>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="11" t="n"/>
       <c r="T16" s="5" t="n"/>
       <c r="U16" s="5" t="n"/>
-      <c r="V16" s="12">
-        <f>IF(OR(H16="",J16=""),"",INT(ROUND(H16*IF(S16="",P16,S16),6)))</f>
-        <v/>
-      </c>
+      <c r="V16" s="12" t="n"/>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
@@ -1025,25 +961,16 @@
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
-      <c r="M17" s="12">
-        <f>IF(J17="","",INT(ROUND(J17*G8,6)))</f>
-        <v/>
-      </c>
+      <c r="M17" s="12" t="n"/>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
-      <c r="P17" s="12">
-        <f>IF(J17="","",INT(ROUND((J17+M17)/2,6)))</f>
-        <v/>
-      </c>
+      <c r="P17" s="12" t="n"/>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="11" t="n"/>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
-      <c r="V17" s="12">
-        <f>IF(OR(H17="",J17=""),"",INT(ROUND(H17*IF(S17="",P17,S17),6)))</f>
-        <v/>
-      </c>
+      <c r="V17" s="12" t="n"/>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
@@ -1073,10 +1000,7 @@
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
-      <c r="V18" s="14">
-        <f>SUM(V11:V17)</f>
-        <v/>
-      </c>
+      <c r="V18" s="14" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
@@ -1217,6 +1141,7 @@
       </c>
     </row>
     <row r="30" ht="6" customHeight="1"/>
+    <row r="31"/>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="22" t="inlineStr">
         <is>
@@ -1329,845 +1254,6 @@
     <mergeCell ref="G8:X8"/>
     <mergeCell ref="K29:P29"/>
   </mergeCells>
-  <conditionalFormatting sqref="H11:H17">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(H11),MOD(H11,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>협 의 단 가 산 정 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계약번호</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>제2026-0312호</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  관련 실정보고</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>실정보고 제3호(2026. 6. 2.)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  낙 찰 률</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="7" t="n">
-        <v>0.87452</v>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="6" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>품명·규격</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>① 변경 당시 단가</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>② ①×낙찰률</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>중간값 (①+②)÷2</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t>협의 단가</t>
-        </is>
-      </c>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>금액</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>PE 이중벽관 D600</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="11" t="n">
-        <v>186500</v>
-      </c>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="12">
-        <f>IF(J11="","",INT(ROUND(J11*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="12">
-        <f>IF(J11="","",INT(ROUND((J11+M11)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="11" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="12">
-        <f>IF(OR(H11="",J11=""),"",INT(ROUND(H11*IF(S11="",P11,S11),6)))</f>
-        <v/>
-      </c>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>집수정 1.2×1.2</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>개소</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="11" t="n">
-        <v>1245000</v>
-      </c>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="12">
-        <f>IF(J12="","",INT(ROUND(J12*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="12">
-        <f>IF(J12="","",INT(ROUND((J12+M12)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="11" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="12">
-        <f>IF(OR(H12="",J12=""),"",INT(ROUND(H12*IF(S12="",P12,S12),6)))</f>
-        <v/>
-      </c>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>가물막이(톤마대)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="11" t="n">
-        <v>38400</v>
-      </c>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="12">
-        <f>IF(J13="","",INT(ROUND(J13*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="12">
-        <f>IF(J13="","",INT(ROUND((J13+M13)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="11" t="n">
-        <v>36000</v>
-      </c>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="12">
-        <f>IF(OR(H13="",J13=""),"",INT(ROUND(H13*IF(S13="",P13,S13),6)))</f>
-        <v/>
-      </c>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="12">
-        <f>IF(J14="","",INT(ROUND(J14*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="12">
-        <f>IF(J14="","",INT(ROUND((J14+M14)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="11" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="12">
-        <f>IF(OR(H14="",J14=""),"",INT(ROUND(H14*IF(S14="",P14,S14),6)))</f>
-        <v/>
-      </c>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="10" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="12">
-        <f>IF(J15="","",INT(ROUND(J15*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="12">
-        <f>IF(J15="","",INT(ROUND((J15+M15)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="11" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="12">
-        <f>IF(OR(H15="",J15=""),"",INT(ROUND(H15*IF(S15="",P15,S15),6)))</f>
-        <v/>
-      </c>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="11" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="12">
-        <f>IF(J16="","",INT(ROUND(J16*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="12">
-        <f>IF(J16="","",INT(ROUND((J16+M16)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="11" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="12">
-        <f>IF(OR(H16="",J16=""),"",INT(ROUND(H16*IF(S16="",P16,S16),6)))</f>
-        <v/>
-      </c>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="12">
-        <f>IF(J17="","",INT(ROUND(J17*G8,6)))</f>
-        <v/>
-      </c>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="12">
-        <f>IF(J17="","",INT(ROUND((J17+M17)/2,6)))</f>
-        <v/>
-      </c>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="11" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="12">
-        <f>IF(OR(H17="",J17=""),"",INT(ROUND(H17*IF(S17="",P17,S17),6)))</f>
-        <v/>
-      </c>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>합        계</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="14">
-        <f>SUM(V11:V17)</f>
-        <v/>
-      </c>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="6" customHeight="1"/>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>※ 협의가 이루어지지 않는 경우의 기준값이 «중간값» 입니다. 협의 결과를 «협의 단가» 에 적습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  협의 일자</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="16" t="n">
-        <v>46185</v>
-      </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  협의 참석자</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>가나시 건설과 박감독 · 예시건설(주) 김철수</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  합의 내용</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>PE관·집수정은 중간값, 가물막이는 협의 단가 36,000원으로 합의</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
-    <row r="26" ht="10" customHeight="1"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="17" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="18" t="inlineStr"/>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>시공자</t>
-        </is>
-      </c>
-      <c r="Q28" s="20" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U28" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="18" t="inlineStr"/>
-      <c r="K29" s="19" t="inlineStr">
-        <is>
-          <t>발주기관</t>
-        </is>
-      </c>
-      <c r="Q29" s="20" t="inlineStr">
-        <is>
-          <t>박감독</t>
-        </is>
-      </c>
-      <c r="U29" s="21" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="94">
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="S14:U14"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="U29:X29"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A32:X32"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="V12:X12"/>
-    <mergeCell ref="G22:X22"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="S17:U17"/>
-    <mergeCell ref="S11:U11"/>
-    <mergeCell ref="G23:X23"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="G24:X24"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A20:X20"/>
-    <mergeCell ref="Q29:T29"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="S16:U16"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="A18:U18"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A27:X27"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="Q28:T28"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="K28:P28"/>
-    <mergeCell ref="V18:X18"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="G8:X8"/>
-    <mergeCell ref="K29:P29"/>
-  </mergeCells>
-  <conditionalFormatting sqref="H11:H17">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(H11),MOD(H11,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/web/public/forms/chg-hyeobui.xlsx
+++ b/web/public/forms/chg-hyeobui.xlsx
@@ -595,7 +595,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
